--- a/app/templates/report/rooming.xlsx
+++ b/app/templates/report/rooming.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7EC31C-930D-468A-9D48-5BF025451B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E9F7B6-188A-4A8D-8E6B-046A3A3DBFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooming" sheetId="1" r:id="rId1"/>
-    <sheet name="Id_type" sheetId="4" state="hidden" r:id="rId2"/>
-    <sheet name="Gender" sheetId="6" state="hidden" r:id="rId3"/>
-    <sheet name="Country" sheetId="5" state="hidden" r:id="rId4"/>
-    <sheet name="Language" sheetId="7" state="hidden" r:id="rId5"/>
+    <sheet name="Rooms" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="Idtype" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="Gender" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="Country" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Language" sheetId="7" state="hidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>ROOMING LIST</t>
   </si>
@@ -156,7 +157,13 @@
     <t>Country_origin.Name</t>
   </si>
   <si>
-    <t>Resource.Code</t>
+    <t>Plazas</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Room.Code</t>
   </si>
 </sst>
 </file>
@@ -166,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -213,6 +220,12 @@
       <b/>
       <sz val="8"/>
       <color indexed="8"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -444,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -513,31 +526,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
@@ -545,7 +542,28 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -644,8 +662,8 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>244849</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>566794</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>314325</xdr:rowOff>
     </xdr:to>
@@ -672,7 +690,7 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="47625" y="47625"/>
-          <a:ext cx="1968874" cy="266700"/>
+          <a:ext cx="2018404" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,9 +707,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -729,7 +747,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -835,7 +853,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -977,7 +995,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -985,49 +1003,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="11" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="28" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="17.7109375" style="12" customWidth="1"/>
-    <col min="20" max="247" width="9.140625" style="5" customWidth="1"/>
-    <col min="248" max="248" width="11.42578125" style="5" customWidth="1"/>
-    <col min="249" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="21.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" style="12" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" style="12" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="17.7109375" style="12" customWidth="1"/>
+    <col min="19" max="246" width="9.140625" style="5" customWidth="1"/>
+    <col min="247" max="247" width="11.42578125" style="5" customWidth="1"/>
+    <col min="248" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="S1" s="31"/>
-    </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="2"/>
+      <c r="R1" s="26"/>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="16">
-        <f>$E$5</f>
+      <c r="F2" s="16">
+        <f>$D$5</f>
         <v>0</v>
       </c>
+      <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1039,166 +1055,172 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" spans="1:19" s="9" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:18" s="9" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>34</v>
       </c>
+      <c r="F3" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="G3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>32</v>
       </c>
+      <c r="I3" s="8" t="s">
+        <v>6</v>
+      </c>
       <c r="J3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="28" t="s">
+      <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="K4" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="L4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="M4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="N4" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="O4" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="29" t="s">
+      <c r="P4" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="Q4" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="25" t="s">
+      <c r="R4" s="32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="19"/>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="22"/>
       <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="date" showInputMessage="1" showErrorMessage="1" sqref="C5:D5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="date" showInputMessage="1" showErrorMessage="1" sqref="B5:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>44927</formula1>
       <formula2>73050</formula2>
     </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{258EF21F-5EC9-4E4F-BCFF-49CA1E9B89AD}"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="D5" xr:uid="{258EF21F-5EC9-4E4F-BCFF-49CA1E9B89AD}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F37FF43C-AE5E-440A-BDD4-C4D5ADF8CD8D}">
+          <x14:formula1>
+            <xm:f>Rooms!$B$3:$B$9999</xm:f>
+          </x14:formula1>
+          <xm:sqref>A5</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70D2ABA-FED4-44BB-9BF8-1BCB7CE78C86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523C847-DC0C-451A-A485-34BBB3550797}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1"/>
@@ -1208,22 +1230,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="33"/>
+      <c r="A1" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>15</v>
+      <c r="B2" s="24" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1232,12 +1254,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3989FD-0CEA-4C54-8F32-C63A200850CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70D2ABA-FED4-44BB-9BF8-1BCB7CE78C86}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1"/>
@@ -1247,22 +1269,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="33"/>
+      <c r="A1" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1271,12 +1293,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B963579A-AE94-4872-A9FB-B9D7241B7D9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3989FD-0CEA-4C54-8F32-C63A200850CD}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1"/>
@@ -1286,22 +1308,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="33"/>
+      <c r="A1" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1310,12 +1332,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BB05A7-C124-442D-BEAC-64F6952880EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B963579A-AE94-4872-A9FB-B9D7241B7D9D}">
   <sheetPr>
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1"/>
@@ -1325,22 +1347,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="27"/>
+    </row>
+    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BB05A7-C124-442D-BEAC-64F6952880EA}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="5" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="33"/>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/templates/report/rooming.xlsx
+++ b/app/templates/report/rooming.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E9F7B6-188A-4A8D-8E6B-046A3A3DBFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2FB1B9-CCB7-49E1-855D-71915E9B3A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,7 +571,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1189,7 +1208,12 @@
       <c r="R5" s="23"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="2">
+  <conditionalFormatting sqref="A5:R9999">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$B5&lt;&gt;$B4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
     <dataValidation type="date" showInputMessage="1" showErrorMessage="1" sqref="B5:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>44927</formula1>
       <formula2>73050</formula2>
@@ -1201,7 +1225,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F37FF43C-AE5E-440A-BDD4-C4D5ADF8CD8D}">
           <x14:formula1>
             <xm:f>Rooms!$B$3:$B$9999</xm:f>

--- a/app/templates/report/rooming.xlsx
+++ b/app/templates/report/rooming.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2FB1B9-CCB7-49E1-855D-71915E9B3A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ECDFFE-9A34-44C0-989E-BD04BE847C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooming" sheetId="1" r:id="rId1"/>
-    <sheet name="Rooms" sheetId="8" state="hidden" r:id="rId2"/>
-    <sheet name="Idtype" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="Gender" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="Country" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="Language" sheetId="7" state="hidden" r:id="rId6"/>
+    <sheet name="_Rooms" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="_Idtype" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="_Gender" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="_Country" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="_Language" sheetId="7" state="hidden" r:id="rId6"/>
+    <sheet name="_Check" sheetId="9" state="hidden" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>ROOMING LIST</t>
   </si>
@@ -163,7 +164,30 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Room.Code</t>
+    <t>Check_in_ok</t>
+  </si>
+  <si>
+    <t>Revisiòn
+Ok</t>
+  </si>
+  <si>
+    <t>Revision_ok</t>
+  </si>
+  <si>
+    <t>Limpieza Fcturada</t>
+  </si>
+  <si>
+    <t>Cleaning_billed</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Check-in
+Ok</t>
+  </si>
+  <si>
+    <t>Resource.Code</t>
   </si>
 </sst>
 </file>
@@ -457,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -564,6 +588,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -571,16 +603,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <border>
         <top style="thin">
@@ -1022,33 +1045,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" style="5" customWidth="1"/>
     <col min="2" max="2" width="10.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" style="11" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" style="12" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="17.7109375" style="12" customWidth="1"/>
-    <col min="19" max="246" width="9.140625" style="5" customWidth="1"/>
-    <col min="247" max="247" width="11.42578125" style="5" customWidth="1"/>
-    <col min="248" max="16384" width="11.42578125" style="5"/>
+    <col min="5" max="7" width="13.140625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" style="12" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" style="12" customWidth="1"/>
+    <col min="12" max="12" width="28.7109375" style="12" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" style="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="17.7109375" style="12" customWidth="1"/>
+    <col min="22" max="249" width="9.140625" style="5" customWidth="1"/>
+    <col min="250" max="250" width="11.42578125" style="5" customWidth="1"/>
+    <col min="251" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="R1" s="26"/>
-    </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U1" s="26"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1064,7 +1088,7 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="16"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1074,8 +1098,11 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" s="9" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:21" s="9" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
@@ -1088,52 +1115,61 @@
       <c r="D3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="K3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="R3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="S3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="T3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="U3" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>12</v>
@@ -1144,97 +1180,90 @@
       <c r="D4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="I4" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="K4" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="L4" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="M4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="N4" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="O4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="34" t="s">
+      <c r="P4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="Q4" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="R4" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="S4" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="35" t="s">
+      <c r="T4" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="U4" s="32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="19"/>
       <c r="B5" s="17"/>
       <c r="C5" s="18"/>
       <c r="D5" s="37"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="22"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="20"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="22"/>
       <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
+      <c r="M5" s="21"/>
       <c r="N5" s="20"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="23"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:R9999">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A5:U9999">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B5&lt;&gt;$B4</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="date" showInputMessage="1" showErrorMessage="1" sqref="B5:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>44927</formula1>
-      <formula2>73050</formula2>
-    </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="D5" xr:uid="{258EF21F-5EC9-4E4F-BCFF-49CA1E9B89AD}"/>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F37FF43C-AE5E-440A-BDD4-C4D5ADF8CD8D}">
-          <x14:formula1>
-            <xm:f>Rooms!$B$3:$B$9999</xm:f>
-          </x14:formula1>
-          <xm:sqref>A5</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -1431,4 +1460,44 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12030276-A529-49DE-962D-5EC1ADD71A7E}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="229" width="9.140625" style="5" customWidth="1"/>
+    <col min="230" max="230" width="11.42578125" style="5" customWidth="1"/>
+    <col min="231" max="16384" width="11.42578125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>
--- a/app/templates/report/rooming.xlsx
+++ b/app/templates/report/rooming.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ECDFFE-9A34-44C0-989E-BD04BE847C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA85B61F-11A7-4560-A176-80C36B6C39EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
-  <si>
-    <t>ROOMING LIST</t>
-  </si>
-  <si>
-    <t>RESERVA:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>Plaza</t>
   </si>
@@ -110,9 +104,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>Booking Id</t>
-  </si>
-  <si>
     <t>Documento</t>
   </si>
   <si>
@@ -164,30 +155,61 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Check_in_ok</t>
-  </si>
-  <si>
-    <t>Revisiòn
-Ok</t>
-  </si>
-  <si>
-    <t>Revision_ok</t>
-  </si>
-  <si>
-    <t>Limpieza Fcturada</t>
-  </si>
-  <si>
-    <t>Cleaning_billed</t>
-  </si>
-  <si>
     <t>Check</t>
   </si>
   <si>
-    <t>Check-in
-Ok</t>
-  </si>
-  <si>
     <t>Resource.Code</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Booking</t>
+  </si>
+  <si>
+    <t>Group_code</t>
+  </si>
+  <si>
+    <t>Datos del residente</t>
+  </si>
+  <si>
+    <t>Rooming list</t>
+  </si>
+  <si>
+    <t>Datos de housing</t>
+  </si>
+  <si>
+    <t>Datos de la plaza</t>
+  </si>
+  <si>
+    <t>Vuelo/Tren</t>
+  </si>
+  <si>
+    <t>Hora
+llegada</t>
+  </si>
+  <si>
+    <t>Hora
+check-in</t>
+  </si>
+  <si>
+    <t>Hora
+recogida</t>
+  </si>
+  <si>
+    <t>Arrival</t>
+  </si>
+  <si>
+    <t>Check_in_time</t>
+  </si>
+  <si>
+    <t>Flight</t>
+  </si>
+  <si>
+    <t>Flight_out</t>
+  </si>
+  <si>
+    <t>Check_out_time</t>
   </si>
 </sst>
 </file>
@@ -197,7 +219,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -212,20 +234,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -253,6 +261,13 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -275,12 +290,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -297,6 +306,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF056D6B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -308,17 +323,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="hair">
@@ -390,11 +394,68 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -407,72 +468,24 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="hair">
+      <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -484,118 +497,118 @@
   <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -682,6 +695,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FF056D6B"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -704,8 +720,8 @@
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>566794</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>433444</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>314325</xdr:rowOff>
     </xdr:to>
@@ -1045,220 +1061,248 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13.140625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.7109375" style="12" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="28.7109375" style="12" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="17.7109375" style="12" customWidth="1"/>
-    <col min="22" max="249" width="9.140625" style="5" customWidth="1"/>
-    <col min="250" max="250" width="11.42578125" style="5" customWidth="1"/>
-    <col min="251" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="10.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="8" customWidth="1"/>
+    <col min="6" max="7" width="10.28515625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="19" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19" style="8" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.7109375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="32.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.7109375" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="17.7109375" style="9" customWidth="1"/>
+    <col min="25" max="252" width="9.140625" style="2" customWidth="1"/>
+    <col min="253" max="253" width="11.42578125" style="2" customWidth="1"/>
+    <col min="254" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="U1" s="26"/>
-    </row>
-    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="21"/>
+    </row>
+    <row r="2" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="35"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="36"/>
+    </row>
+    <row r="3" spans="1:24" s="6" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="16">
-        <f>$D$5</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-    </row>
-    <row r="3" spans="1:21" s="9" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="N3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="P3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P4" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="13" t="s">
+      <c r="V4" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="P4" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="T4" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="39"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="31"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="23"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:U9999">
+  <conditionalFormatting sqref="A5:X9999">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$B5&lt;&gt;$B4</formula>
+      <formula>$D5&lt;&gt;$D4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1275,30 +1319,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="5" customWidth="1"/>
-    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
-    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
-    <col min="232" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="2" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="2" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="27"/>
-    </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>40</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1314,30 +1358,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="5" customWidth="1"/>
-    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
-    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
-    <col min="232" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="2" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="2" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="27"/>
-    </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>15</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1353,30 +1397,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="5" customWidth="1"/>
-    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
-    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
-    <col min="232" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="2" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="2" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="27"/>
-    </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>15</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1392,30 +1436,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="5" customWidth="1"/>
-    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
-    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
-    <col min="232" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="2" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="2" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="27"/>
-    </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>15</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1431,30 +1475,30 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="5" customWidth="1"/>
-    <col min="3" max="230" width="9.140625" style="5" customWidth="1"/>
-    <col min="231" max="231" width="11.42578125" style="5" customWidth="1"/>
-    <col min="232" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="2" customWidth="1"/>
+    <col min="3" max="230" width="9.140625" style="2" customWidth="1"/>
+    <col min="231" max="231" width="11.42578125" style="2" customWidth="1"/>
+    <col min="232" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="27"/>
-    </row>
-    <row r="2" spans="1:2" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>15</v>
+    <row r="1" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="22"/>
+    </row>
+    <row r="2" spans="1:2" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1470,29 +1514,29 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="229" width="9.140625" style="5" customWidth="1"/>
-    <col min="230" max="230" width="11.42578125" style="5" customWidth="1"/>
-    <col min="231" max="16384" width="11.42578125" style="5"/>
+    <col min="1" max="1" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="229" width="9.140625" style="2" customWidth="1"/>
+    <col min="230" max="230" width="11.42578125" style="2" customWidth="1"/>
+    <col min="231" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="10" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>15</v>
+    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="b">
+      <c r="A3" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="b">
+      <c r="A4" s="24" t="b">
         <v>1</v>
       </c>
     </row>
